--- a/Result/profitability/8937.xlsx
+++ b/Result/profitability/8937.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>-0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.145</v>
+        <v>-0.115</v>
       </c>
       <c r="N2" t="n">
-        <v>-28.62375</v>
+        <v>-25.46875</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.24</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0675</v>
+        <v>-0.10625</v>
       </c>
       <c r="N3" t="n">
-        <v>-26.205</v>
+        <v>-23.53125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.065</v>
+        <v>-0.07250000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-24.595</v>
+        <v>-19.3875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.21</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.08125</v>
+        <v>0.125</v>
       </c>
       <c r="N5" t="n">
-        <v>-21.755</v>
+        <v>-12.92875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0.14125</v>
+        <v>0.09625</v>
       </c>
       <c r="N6" t="n">
-        <v>-14.66875</v>
+        <v>-0.07499999999999907</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>-0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08750000000000002</v>
+        <v>-0.04125</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.668749999999999</v>
+        <v>13.455</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02374999999999999</v>
+        <v>-0.03249999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>12.285</v>
+        <v>11.75375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8937</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>231</v>
+      </c>
+      <c r="D75" t="n">
+        <v>182</v>
+      </c>
+      <c r="E75" t="n">
+        <v>49</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-14.86%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-17</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-51</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-59</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1475</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-27.90875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1673887357227255</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9217877094972067</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.427329694764504</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
